--- a/data/S2002_03_FINAL.xlsx
+++ b/data/S2002_03_FINAL.xlsx
@@ -27,8 +27,11 @@
     <sheet name="SERIES" sheetId="18" state="visible" r:id="rId18"/>
     <sheet name="CLUBS" sheetId="19" state="visible" r:id="rId19"/>
     <sheet name="META" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="TODO" sheetId="21" state="visible" r:id="rId21"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'TODO'!$A$1:$F$4</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -36,7 +39,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -51,8 +54,12 @@
       <name val="Arial"/>
       <b val="1"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -69,6 +76,11 @@
         <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00305496"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -82,11 +94,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -10154,7 +10172,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10198,6 +10216,57 @@
       <c r="D2" t="inlineStr">
         <is>
           <t>DS-PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0021</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida: SYSTEM NODE_S2002_03_0021 'Baráž o Extraligu' (L15, parent=NODE_S2002_03_0001) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0028</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida: SYSTEM NODE_S2002_03_0028 'Baráž o I.ligu' (L25, parent=NODE_S2002_03_0003) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0042</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida: SYSTEM NODE_S2002_03_0042 'O postup do I.ligy' (L25, parent=NODE_S2002_03_0036) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
         </is>
       </c>
     </row>
@@ -13180,8 +13249,6 @@
         </is>
       </c>
     </row>
-    <row r="71"/>
-    <row r="72"/>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
@@ -13261,7 +13328,6 @@
         </is>
       </c>
     </row>
-    <row r="80"/>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
@@ -27261,6 +27327,127 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="88" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>typ</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>popis</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>vyřešeno? (ANO/ne)</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>poznámka kolegy</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>pyramida</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0021</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>SYSTEM NODE_S2002_03_0021 'Baráž o Extraligu' (L15, parent=NODE_S2002_03_0001) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>pyramida</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0028</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>SYSTEM NODE_S2002_03_0028 'Baráž o I.ligu' (L25, parent=NODE_S2002_03_0003) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>pyramida</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0042</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>SYSTEM NODE_S2002_03_0042 'O postup do I.ligy' (L25, parent=NODE_S2002_03_0036) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F4"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/data/S2002_03_FINAL.xlsx
+++ b/data/S2002_03_FINAL.xlsx
@@ -30,7 +30,7 @@
     <sheet name="TODO" sheetId="21" state="visible" r:id="rId21"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'TODO'!$A$1:$F$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'TODO'!$A$1:$F$31</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -7683,11 +7683,6 @@
           <t>CLUB_S2002_03_0179</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>CLUB_S2001_02_0068</t>
-        </is>
-      </c>
       <c r="U6" t="inlineStr">
         <is>
           <t>reorganizace</t>
@@ -8053,11 +8048,6 @@
           <t>CLUB_S2002_03_0184</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>CLUB_S2001_02_0068</t>
-        </is>
-      </c>
       <c r="U12" t="inlineStr">
         <is>
           <t>setrval</t>
@@ -8103,11 +8093,6 @@
       <c r="Q13" t="inlineStr">
         <is>
           <t>CLUB_S2002_03_0186</t>
-        </is>
-      </c>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>CLUB_S2001_02_0068</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -10172,7 +10157,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10220,14 +10205,9 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>NODE_S2002_03_0021</t>
-        </is>
-      </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>[TBD] pyramida: SYSTEM NODE_S2002_03_0021 'Baráž o Extraligu' (L15, parent=NODE_S2002_03_0001) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -10237,14 +10217,9 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>NODE_S2002_03_0028</t>
-        </is>
-      </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>[TBD] pyramida: SYSTEM NODE_S2002_03_0028 'Baráž o I.ligu' (L25, parent=NODE_S2002_03_0003) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -10254,17 +10229,336 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>NODE_S2002_03_0042</t>
-        </is>
-      </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>[TBD] pyramida: SYSTEM NODE_S2002_03_0042 'O postup do I.ligy' (L25, parent=NODE_S2002_03_0036) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'České Budějovice' → 'Slezan Opava' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'HK Lev Slaný' → 'Slaný' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vlci Jablonec nad Nisou' → 'Jablonec nad Nisou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'NED Hockey Nymburk' → 'Nymburk' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'VHS HC Benešov' → 'Benešov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Teplice' → 'Stadion Litoměřice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Prostějov' → 'Nový Bydžov' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Havlíčkův Brod' → 'Uherské Hradiště' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'VSK Technika Brno' → 'Technika Brno' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
@@ -13249,6 +13543,8 @@
         </is>
       </c>
     </row>
+    <row r="71"/>
+    <row r="72"/>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
@@ -13279,6 +13575,11 @@
           <t>I.ČNHL (12 CZ) + SNHL (12 SVK)</t>
         </is>
       </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0001</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -13291,6 +13592,11 @@
           <t>Kvalifikace o II.ligu</t>
         </is>
       </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0003</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -13303,6 +13609,11 @@
           <t>Krajské přebory (nové velké kraje!)</t>
         </is>
       </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0003</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -13315,6 +13626,11 @@
           <t>I.třída / I.B třída / Krajská soutěž</t>
         </is>
       </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0036</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -13328,6 +13644,7 @@
         </is>
       </c>
     </row>
+    <row r="80"/>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
@@ -16605,12 +16922,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Třinec = TJ TŽ VŘSR Třinec (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. **TŽ** = Třinecké železárny. **VŘSR** = Velka řijnova socialisticka revoluce (pojmenovani po vyroci VŘSR 1917). city Třinec.</t>
+          <t>Třinec = TJ TŽ VŘSR Třinec (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. **TŽ** = Třinecké železárny. **VŘSR** = Velka řijnova socialisticka revoluce (pojmenovani po vyroci VŘSR 1917). city Třinec. || TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>TŽ VŘSR Třinec</t>
+          <t>Třinec</t>
         </is>
       </c>
     </row>
@@ -16689,12 +17006,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Plzeň</t>
+          <t>České Budějovice</t>
         </is>
       </c>
     </row>
@@ -17161,12 +17478,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Chomutov = KLH VT VTJ Chomutov (Wiki D42 - registr ustavy 04/2026). Severocesky/Ustecky kraj. **KLH VT VTJ** = post-revolucni nazev (KLH = klub lední hokej, VT = vrcholový tým, VTJ = Vojenská tělovýchovná jednota). city Chomutov.</t>
+          <t>Chomutov = KLH VT VTJ Chomutov (Wiki D42 - registr ustavy 04/2026). Severocesky/Ustecky kraj. **KLH VT VTJ** = post-revolucni nazev (KLH = klub lední hokej, VT = vrcholový tým, VTJ = Vojenská tělovýchovná jednota). city Chomutov. || TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>KLH VT VTJ Chomutov</t>
+          <t>Chomutov</t>
         </is>
       </c>
     </row>
@@ -17208,12 +17525,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov.</t>
+          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov. || TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Chomutov</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
     </row>
@@ -17413,12 +17730,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Slavoj České Budějovice B (Wiki D42 - registr ustavy 04/2026). B-tym hlavni Motor CB chain. city České Budějovice.</t>
+          <t>Slavoj České Budějovice B (Wiki D42 - registr ustavy 04/2026). B-tym hlavni Motor CB chain. city České Budějovice. || TBD: city 'České Budějovice' → 'Slezan Opava' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Slezan Opava</t>
         </is>
       </c>
     </row>
@@ -17460,12 +17777,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Žďár nL Sázavou = TJ Žďas Žďár nL Sázavou (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihlavsky kraj. **ŽĎAS** = Žďárské strojírny a slévárny (kovaci/lisovaci stroje). 'Žďas' = lokalní pravopis. city Žďár nad Sázavou.</t>
+          <t>Žďár nL Sázavou = TJ Žďas Žďár nL Sázavou (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihlavsky kraj. **ŽĎAS** = Žďárské strojírny a slévárny (kovaci/lisovaci stroje). 'Žďas' = lokalní pravopis. city Žďár nad Sázavou. || TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Žďas Žďár nad Sázavou</t>
+          <t>Žďár nad Sázavou</t>
         </is>
       </c>
     </row>
@@ -17591,12 +17908,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov.</t>
+          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov. || TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
     </row>
@@ -18569,12 +18886,12 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Klášterec nad Ohří = Sokol Klášterec (Wiki D42 - registr ustavy 04/2026). Severocesky kraj (okres Chomutov). HC Klášterec dnes mensi soutez. city Klášterec nad Ohří.</t>
+          <t>Klášterec nad Ohří = Sokol Klášterec (Wiki D42 - registr ustavy 04/2026). Severocesky kraj (okres Chomutov). HC Klášterec dnes mensi soutez. city Klášterec nad Ohří. || TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Klášterec</t>
+          <t>Klášterec nad Ohří</t>
         </is>
       </c>
     </row>
@@ -18863,12 +19180,12 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Slaný = HK Lev Slaný (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Kladno). '(II)' = druzstvo II. city Slaný.</t>
+          <t>Slaný = HK Lev Slaný (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Kladno). '(II)' = druzstvo II. city Slaný. || TBD: city 'HK Lev Slaný' → 'Slaný' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>HK Lev Slaný</t>
+          <t>Slaný</t>
         </is>
       </c>
     </row>
@@ -19036,12 +19353,12 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec.</t>
+          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec. || TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Vajgar Jindřichův Hradec</t>
+          <t>Jindřichův Hradec</t>
         </is>
       </c>
     </row>
@@ -19078,12 +19395,12 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Jablonec nad Nisou = HC Vlci Jablonec nL Nisou (Wiki D42 - registr ustavy 04/2026). Severocesky/Liberecky kraj. city Jablonec nad Nisou.</t>
+          <t>Jablonec nad Nisou = HC Vlci Jablonec nL Nisou (Wiki D42 - registr ustavy 04/2026). Severocesky/Liberecky kraj. city Jablonec nad Nisou. || TBD: city 'Vlci Jablonec nad Nisou' → 'Jablonec nad Nisou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Vlci Jablonec nad Nisou</t>
+          <t>Jablonec nad Nisou</t>
         </is>
       </c>
     </row>
@@ -19246,12 +19563,12 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Nymburk = NED Hockey Nymburk (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj. Post-revolucni. city Nymburk.</t>
+          <t>Nymburk = NED Hockey Nymburk (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj. Post-revolucni. city Nymburk. || TBD: city 'NED Hockey Nymburk' → 'Nymburk' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>NED Hockey Nymburk</t>
+          <t>Nymburk</t>
         </is>
       </c>
     </row>
@@ -20415,12 +20732,12 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Benešov = HC VHS Benešov (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj. **VHS** = Vodohospodářské stavby. city Benešov.</t>
+          <t>Benešov = HC VHS Benešov (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj. **VHS** = Vodohospodářské stavby. city Benešov. || TBD: city 'VHS HC Benešov' → 'Benešov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>VHS HC Benešov</t>
+          <t>Benešov</t>
         </is>
       </c>
     </row>
@@ -21055,12 +21372,12 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou.</t>
+          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou. || TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach] || TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>Lokomotiva  Veselí nad Moravou</t>
+          <t>Veselí nad Lužnicí</t>
         </is>
       </c>
     </row>
@@ -21186,12 +21503,12 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>Plzeň</t>
+          <t>České Budějovice</t>
         </is>
       </c>
     </row>
@@ -21480,12 +21797,12 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>Oprava city: „Testroj Teplice" → „Teplice" (Testroj = závod). || Sokol Testroj Teplice 52/53 - hlavni klub (Testroj podnik). Teplice = HC Stadion Teplice (Wiki D42 - registr 04/2026). Genealogie: Technomat Teplice (49/50, podnik Technomat) -&gt; Sokol Testroj Teplice (52/53, Testroj/Somet podnik) -&gt; Tatran Teplice (53/54+ DSO reforma). Plus Sklarny Retenice paralelni klub (skladlo se 55/56 s Tatranem Teplice). Dnesni klub HC Stadion Teplice. Patterns: Technomat Teplice, Sokol Testroj, Tatran Teplice, Sklárny Řetenice. city Teplice. || Sokol Testroj Teplice 52/53 (20_Ústecký okresni). Testroj = podnik (puvodne Technomat). Teplice = HC Stadion Teplice / HC Teplice Huskies (Wiki D42 + hokej.cz - 04/2026). Genealogie: Klub zalozen 1945. Technomat Teplice (1949-50, podnikovy klub Technomat) -&gt; Sokol Testroj (1952) -&gt; Tatran Teplice (1953+, DSO reforma) -&gt;... -&gt; HC Stadion Teplice (do 2007, klub rozpusten po sestupu kvuli neprovozuschopnosti ZS) -&gt; HC Teplice Huskies (2018+ novy mladeznicky klub, novy zimni stadion otevren 2019). city Teplice. POZOR: Teplice nad Metují = JINE MESTO (Královehradecky kraj, Slavoj Teplice nL Metují) - separate od stredoceskych Teplic. || Teplice = HC Stadion Teplice (1945-2007) -&gt; HC Teplice Huskies (2019-dnes) (Pavlovo upresneni 04/2026 + Wiki + FK Teplice paralelni vyvoj). Genealogie podle paralelni fotbalove linie: 1945 zalozeni -&gt; 1948 Sokol -&gt; 1949 Technomat (podnik OD - obchodni dum) -&gt; 1951 Vodotechna (vodni stavby) -&gt; 1952 Ingstav (inzenyrska stavba) -&gt; 1953 Tatran Teplice (DSO reforma) -&gt; 1960 Slovan -&gt; 1966 Sklo Union -&gt; po 1991 menici se nazvy -&gt; 2007 PRERUSENI provozu - nositel hokejove tradice mesta pokracuje v Teplice Huskies (2019) -&gt; 2010 zbytky presun do Biliny -&gt; 2019 obnoveni HC Teplice Huskies (novy ZS). Patterns: Technomat Teplice, Vodotechna, Tatran Teplice, Slovan Teplice. Plus mensi paralelni kluby v 50. letech: Sokol Testroj/Somet/Ingstav, Sokol Sklarny Retenice, Jiskra Retenice (1955 sloucena s Tatranem), Spartak Trnovany, Banik Teplice, Lokomotiva Teplice, Tatran Sobedruhy. Retenice + Trnovany + Sobedruhy = mestske casti Teplic (Retenice oficialne od 1963). Sklarny Retenice = city Teplice. || Teplice (Wiki D42 - registr ustavy 04/2026). Hlavni chain HC Stadion Teplice (1945-2007) -&gt; Teplice Huskies (2019-): Technomat -&gt; Vodotechna -&gt; Ingstav -&gt; Tatran (1953) -&gt; Slovan (1960) -&gt; Sklo Union (1966). Plus mestske casti: Retenice (sklarny od 1890), Trnovany, Sobedruhy. city Teplice.</t>
+          <t>Oprava city: „Testroj Teplice" → „Teplice" (Testroj = závod). || Sokol Testroj Teplice 52/53 - hlavni klub (Testroj podnik). Teplice = HC Stadion Teplice (Wiki D42 - registr 04/2026). Genealogie: Technomat Teplice (49/50, podnik Technomat) -&gt; Sokol Testroj Teplice (52/53, Testroj/Somet podnik) -&gt; Tatran Teplice (53/54+ DSO reforma). Plus Sklarny Retenice paralelni klub (skladlo se 55/56 s Tatranem Teplice). Dnesni klub HC Stadion Teplice. Patterns: Technomat Teplice, Sokol Testroj, Tatran Teplice, Sklárny Řetenice. city Teplice. || Sokol Testroj Teplice 52/53 (20_Ústecký okresni). Testroj = podnik (puvodne Technomat). Teplice = HC Stadion Teplice / HC Teplice Huskies (Wiki D42 + hokej.cz - 04/2026). Genealogie: Klub zalozen 1945. Technomat Teplice (1949-50, podnikovy klub Technomat) -&gt; Sokol Testroj (1952) -&gt; Tatran Teplice (1953+, DSO reforma) -&gt;... -&gt; HC Stadion Teplice (do 2007, klub rozpusten po sestupu kvuli neprovozuschopnosti ZS) -&gt; HC Teplice Huskies (2018+ novy mladeznicky klub, novy zimni stadion otevren 2019). city Teplice. POZOR: Teplice nad Metují = JINE MESTO (Královehradecky kraj, Slavoj Teplice nL Metují) - separate od stredoceskych Teplic. || Teplice = HC Stadion Teplice (1945-2007) -&gt; HC Teplice Huskies (2019-dnes) (Pavlovo upresneni 04/2026 + Wiki + FK Teplice paralelni vyvoj). Genealogie podle paralelni fotbalove linie: 1945 zalozeni -&gt; 1948 Sokol -&gt; 1949 Technomat (podnik OD - obchodni dum) -&gt; 1951 Vodotechna (vodni stavby) -&gt; 1952 Ingstav (inzenyrska stavba) -&gt; 1953 Tatran Teplice (DSO reforma) -&gt; 1960 Slovan -&gt; 1966 Sklo Union -&gt; po 1991 menici se nazvy -&gt; 2007 PRERUSENI provozu - nositel hokejove tradice mesta pokracuje v Teplice Huskies (2019) -&gt; 2010 zbytky presun do Biliny -&gt; 2019 obnoveni HC Teplice Huskies (novy ZS). Patterns: Technomat Teplice, Vodotechna, Tatran Teplice, Slovan Teplice. Plus mensi paralelni kluby v 50. letech: Sokol Testroj/Somet/Ingstav, Sokol Sklarny Retenice, Jiskra Retenice (1955 sloucena s Tatranem), Spartak Trnovany, Banik Teplice, Lokomotiva Teplice, Tatran Sobedruhy. Retenice + Trnovany + Sobedruhy = mestske casti Teplic (Retenice oficialne od 1963). Sklarny Retenice = city Teplice. || Teplice (Wiki D42 - registr ustavy 04/2026). Hlavni chain HC Stadion Teplice (1945-2007) -&gt; Teplice Huskies (2019-): Technomat -&gt; Vodotechna -&gt; Ingstav -&gt; Tatran (1953) -&gt; Slovan (1960) -&gt; Sklo Union (1966). Plus mestske casti: Retenice (sklarny od 1890), Trnovany, Sobedruhy. city Teplice. || TBD: city 'Teplice' → 'Stadion Litoměřice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Stadion Litoměřice</t>
         </is>
       </c>
     </row>
@@ -21522,12 +21839,12 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>Ústí nad Labem = TJ Slovan NV Ústí nL Labem (Wiki D42 - registr ustavy 04/2026). **NV** = Národní výbor (správní orgán). city Ústí nad Labem.</t>
+          <t>Ústí nad Labem = TJ Slovan NV Ústí nL Labem (Wiki D42 - registr ustavy 04/2026). **NV** = Národní výbor (správní orgán). city Ústí nad Labem. || TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>NV Ústí nad Labem</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
     </row>
@@ -23395,12 +23712,12 @@
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov.</t>
+          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov. || TBD: city 'Prostějov' → 'Nový Bydžov' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Nový Bydžov</t>
         </is>
       </c>
     </row>
@@ -23719,14 +24036,9 @@
           <t>L40</t>
         </is>
       </c>
-      <c r="H173" t="inlineStr">
-        <is>
-          <t>CLUB_S2001_02_0068</t>
-        </is>
-      </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>Jiskra Havlíčkův Brod = HC Rebel HB (Wiki D42 - registr ustavy 04/2026). city Havlíčkův Brod.</t>
+          <t>Jiskra Havlíčkův Brod = HC Rebel HB (Wiki D42 - registr ustavy 04/2026). city Havlíčkův Brod. || TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
@@ -23924,19 +24236,14 @@
           <t>L40</t>
         </is>
       </c>
-      <c r="H178" t="inlineStr">
-        <is>
-          <t>CLUB_S2001_02_0068</t>
-        </is>
-      </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>Jiskra Havlíčkův Brod = HC Rebel HB (Wiki D42 - registr ustavy 04/2026). city Havlíčkův Brod.</t>
+          <t>Jiskra Havlíčkův Brod = HC Rebel HB (Wiki D42 - registr ustavy 04/2026). city Havlíčkův Brod. || TBD: city 'Havlíčkův Brod' → 'Uherské Hradiště' (odvozeno z názvu klubu) [polish_almanach] || TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>Havlíčkův Brod</t>
+          <t>Uherské Hradiště</t>
         </is>
       </c>
     </row>
@@ -23966,14 +24273,9 @@
           <t>L40</t>
         </is>
       </c>
-      <c r="H179" t="inlineStr">
-        <is>
-          <t>CLUB_S2001_02_0068</t>
-        </is>
-      </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>Jiskra Havlíčkův Brod = HC Rebel HB (Wiki D42 - registr ustavy 04/2026). city Havlíčkův Brod.</t>
+          <t>Jiskra Havlíčkův Brod = HC Rebel HB (Wiki D42 - registr ustavy 04/2026). city Havlíčkův Brod. || TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
@@ -24247,12 +24549,12 @@
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>Brno = VSK Technika Brno (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj. **VSK Technika** = Vysokoškolský sportovní klub (VUT Brno). city Brno.</t>
+          <t>Brno = VSK Technika Brno (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj. **VSK Technika** = Vysokoškolský sportovní klub (VUT Brno). city Brno. || TBD: city 'VSK Technika Brno' → 'Technika Brno' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t>VSK Technika Brno</t>
+          <t>Technika Brno</t>
         </is>
       </c>
     </row>
@@ -27333,11 +27635,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
     <col width="88" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
@@ -27382,21 +27684,19 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>pyramida</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>NODE_S2002_03_0021</t>
+          <t>CLUB_S2002_03_0004</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>SYSTEM NODE_S2002_03_0021 'Baráž o Extraligu' (L15, parent=NODE_S2002_03_0001) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
+          <t>TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -27404,21 +27704,19 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>pyramida</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>NODE_S2002_03_0028</t>
+          <t>CLUB_S2002_03_0006</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>SYSTEM NODE_S2002_03_0028 'Baráž o I.ligu' (L25, parent=NODE_S2002_03_0003) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
+          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -27426,24 +27724,562 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>pyramida</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>NODE_S2002_03_0042</t>
+          <t>CLUB_S2002_03_0017</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>SYSTEM NODE_S2002_03_0042 'O postup do I.ligy' (L25, parent=NODE_S2002_03_0036) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
+          <t>TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0018</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0023</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'České Budějovice' → 'Slezan Opava' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0024</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0027</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0055</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0063</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'HK Lev Slaný' → 'Slaný' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0065</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0067</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0069</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'Vlci Jablonec nad Nisou' → 'Jablonec nad Nisou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0073</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'NED Hockey Nymburk' → 'Nymburk' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0101</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'VHS HC Benešov' → 'Benešov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0116</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0116</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0119</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0126</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'Teplice' → 'Stadion Litoměřice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0127</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0149</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0160</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0164</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0171</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'Prostějov' → 'Nový Bydžov' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0176</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0179</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0184</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'Havlíčkův Brod' → 'Uherské Hradiště' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0184</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0186</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0188</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0193</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'VSK Technika Brno' → 'Technika Brno' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F4"/>
+  <autoFilter ref="A1:F31"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/S2002_03_FINAL.xlsx
+++ b/data/S2002_03_FINAL.xlsx
@@ -30,7 +30,7 @@
     <sheet name="TODO" sheetId="21" state="visible" r:id="rId21"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'TODO'!$A$1:$F$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'TODO'!$A$1:$F$22</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -10157,7 +10157,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D32"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10219,7 +10219,7 @@
     <row r="4">
       <c r="C4" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -10231,7 +10231,7 @@
     <row r="5">
       <c r="C5" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -10243,7 +10243,7 @@
     <row r="6">
       <c r="C6" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -10255,7 +10255,7 @@
     <row r="7">
       <c r="C7" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'České Budějovice' → 'Slezan Opava' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'HK Lev Slaný' → 'Slaný' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -10267,7 +10267,7 @@
     <row r="8">
       <c r="C8" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -10279,7 +10279,7 @@
     <row r="9">
       <c r="C9" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -10291,7 +10291,7 @@
     <row r="10">
       <c r="C10" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vlci Jablonec nad Nisou' → 'Jablonec nad Nisou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -10303,7 +10303,7 @@
     <row r="11">
       <c r="C11" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'HK Lev Slaný' → 'Slaný' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'NED Hockey Nymburk' → 'Nymburk' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -10315,7 +10315,7 @@
     <row r="12">
       <c r="C12" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'VHS HC Benešov' → 'Benešov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -10327,7 +10327,7 @@
     <row r="13">
       <c r="C13" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -10339,7 +10339,7 @@
     <row r="14">
       <c r="C14" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vlci Jablonec nad Nisou' → 'Jablonec nad Nisou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -10351,7 +10351,7 @@
     <row r="15">
       <c r="C15" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'NED Hockey Nymburk' → 'Nymburk' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -10363,7 +10363,7 @@
     <row r="16">
       <c r="C16" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'VHS HC Benešov' → 'Benešov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -10375,7 +10375,7 @@
     <row r="17">
       <c r="C17" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -10387,7 +10387,7 @@
     <row r="18">
       <c r="C18" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -10399,7 +10399,7 @@
     <row r="19">
       <c r="C19" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -10411,7 +10411,7 @@
     <row r="20">
       <c r="C20" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Teplice' → 'Stadion Litoměřice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -10423,7 +10423,7 @@
     <row r="21">
       <c r="C21" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -10435,7 +10435,7 @@
     <row r="22">
       <c r="C22" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -10447,118 +10447,10 @@
     <row r="23">
       <c r="C23" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'VSK Technika Brno' → 'Technika Brno' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Prostějov' → 'Nový Bydžov' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Havlíčkův Brod' → 'Uherské Hradiště' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'VSK Technika Brno' → 'Technika Brno' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
@@ -10575,7 +10467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K84"/>
+  <dimension ref="A1:L84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10634,6 +10526,11 @@
           <t>note</t>
         </is>
       </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>prev_node_id</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -10676,6 +10573,11 @@
           <t>14 týmů (5 stat sloupců): základ + QF/SF/finále + baráž. Mistr: HC Slavia Praha.</t>
         </is>
       </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>NODE_S2001_02_0001</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -10723,6 +10625,11 @@
           <t>Vítězové 4 skupin II.ligy. Dvoukolově. Top 2 do I.ligy.</t>
         </is>
       </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>NODE_S2001_02_0002</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -10765,6 +10672,11 @@
           <t>I.ČNHL: základ + playoff (QF/SF/finále/O 3.) + O 5.-8. + o udržení. I.SNHL (12). Kval o I.ligu.</t>
         </is>
       </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>NODE_S2001_02_0003</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -10807,6 +10719,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>NODE_S2001_02_0004</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -10849,6 +10766,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>NODE_S2001_02_0005</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -10891,6 +10813,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>NODE_S2001_02_0006</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -10933,6 +10860,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>NODE_S2001_02_0007</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -10975,6 +10907,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>NODE_S2001_02_0008</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -11017,6 +10954,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>NODE_S2001_02_0009</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -11059,6 +11001,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>NODE_S2001_02_0010</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -11101,6 +11048,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>NODE_S2001_02_0011</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -11143,6 +11095,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>NODE_S2001_02_0012</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -11185,6 +11142,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>NODE_S2001_02_0013</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -11227,6 +11189,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>NODE_S2001_02_0014</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -11269,6 +11236,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>NODE_S2001_02_0015</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -11311,6 +11283,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>NODE_S2001_02_0016</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -11353,6 +11330,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>NODE_S2001_02_0017</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -11395,6 +11377,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>NODE_S2001_02_0018</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -11437,6 +11424,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>NODE_S2001_02_0019</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -11479,6 +11471,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>NODE_S2001_02_0020</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -11521,6 +11518,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>NODE_S2001_02_0021</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -11563,6 +11565,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>NODE_S2001_02_0022</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -11605,6 +11612,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>NODE_S2001_02_0023</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -11647,6 +11659,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>NODE_S2001_02_0024</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -11689,6 +11706,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>NODE_S2001_02_0025</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -11731,6 +11753,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>NODE_S2001_02_0026</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -11773,6 +11800,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>NODE_S2001_02_0027</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -11815,6 +11847,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>NODE_S2001_02_0028</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -11862,6 +11899,11 @@
           <t>Kvalifikace o postup do II.ligy</t>
         </is>
       </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>NODE_S2001_02_0029</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -11904,6 +11946,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>NODE_S2001_02_0034</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -12030,6 +12077,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>NODE_S2001_02_0038</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -12072,6 +12124,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>NODE_S2001_02_0039</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -12156,6 +12213,11 @@
           <t>II.liga: 2 skupiny + finále + o postup do I.ligy.</t>
         </is>
       </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>NODE_S2001_02_0041</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -12198,6 +12260,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>NODE_S2001_02_0042</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -12240,6 +12307,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>NODE_S2001_02_0043</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -12282,6 +12354,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>NODE_S2001_02_0044</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -12324,6 +12401,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>NODE_S2001_02_0045</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -12366,6 +12448,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>NODE_S2001_02_0046</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -12408,6 +12495,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>NODE_S2001_02_0047</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -12450,6 +12542,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>NODE_S2001_02_0048</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -12492,6 +12589,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>NODE_S2001_02_0049</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -12618,6 +12720,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>NODE_S2001_02_0051</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -12660,6 +12767,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>NODE_S2001_02_0052</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -12702,6 +12814,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>NODE_S2001_02_0056</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -12744,6 +12861,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>NODE_S2001_02_0058</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -12786,6 +12908,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>NODE_S2001_02_0061</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -12996,6 +13123,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>NODE_S2001_02_0071</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -13164,6 +13296,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>NODE_S2001_02_0077</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -13458,6 +13595,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>NODE_S2001_02_0084</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -13500,6 +13642,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>NODE_S2001_02_0086</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -13540,6 +13687,11 @@
       <c r="J70" t="inlineStr">
         <is>
           <t>complete</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>NODE_S2001_02_0087</t>
         </is>
       </c>
     </row>
@@ -13563,6 +13715,11 @@
           <t>I.liga (10 týmů, jeden stůl)</t>
         </is>
       </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>L10</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -13580,6 +13737,11 @@
           <t>NODE_S2002_03_0001</t>
         </is>
       </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -13597,6 +13759,11 @@
           <t>NODE_S2002_03_0003</t>
         </is>
       </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>L25</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -13614,6 +13781,11 @@
           <t>NODE_S2002_03_0003</t>
         </is>
       </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>L30</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -13631,6 +13803,11 @@
           <t>NODE_S2002_03_0036</t>
         </is>
       </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -13641,6 +13818,11 @@
       <c r="B79" t="inlineStr">
         <is>
           <t>Okresní přebory (jen registr)</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>okresní</t>
         </is>
       </c>
     </row>
@@ -17006,12 +17188,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Plzeň</t>
         </is>
       </c>
     </row>
@@ -17525,12 +17707,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov. || TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov.</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Chomutov</t>
         </is>
       </c>
     </row>
@@ -17730,12 +17912,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Slavoj České Budějovice B (Wiki D42 - registr ustavy 04/2026). B-tym hlavni Motor CB chain. city České Budějovice. || TBD: city 'České Budějovice' → 'Slezan Opava' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Slavoj České Budějovice B (Wiki D42 - registr ustavy 04/2026). B-tym hlavni Motor CB chain. city České Budějovice.</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Slezan Opava</t>
+          <t>České Budějovice</t>
         </is>
       </c>
     </row>
@@ -17908,12 +18090,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov. || TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov.</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Prostějov</t>
         </is>
       </c>
     </row>
@@ -21372,12 +21554,12 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou. || TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach] || TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou. || TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>Veselí nad Lužnicí</t>
+          <t>Veselí nad Moravou</t>
         </is>
       </c>
     </row>
@@ -21503,12 +21685,12 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Plzeň</t>
         </is>
       </c>
     </row>
@@ -21797,12 +21979,12 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>Oprava city: „Testroj Teplice" → „Teplice" (Testroj = závod). || Sokol Testroj Teplice 52/53 - hlavni klub (Testroj podnik). Teplice = HC Stadion Teplice (Wiki D42 - registr 04/2026). Genealogie: Technomat Teplice (49/50, podnik Technomat) -&gt; Sokol Testroj Teplice (52/53, Testroj/Somet podnik) -&gt; Tatran Teplice (53/54+ DSO reforma). Plus Sklarny Retenice paralelni klub (skladlo se 55/56 s Tatranem Teplice). Dnesni klub HC Stadion Teplice. Patterns: Technomat Teplice, Sokol Testroj, Tatran Teplice, Sklárny Řetenice. city Teplice. || Sokol Testroj Teplice 52/53 (20_Ústecký okresni). Testroj = podnik (puvodne Technomat). Teplice = HC Stadion Teplice / HC Teplice Huskies (Wiki D42 + hokej.cz - 04/2026). Genealogie: Klub zalozen 1945. Technomat Teplice (1949-50, podnikovy klub Technomat) -&gt; Sokol Testroj (1952) -&gt; Tatran Teplice (1953+, DSO reforma) -&gt;... -&gt; HC Stadion Teplice (do 2007, klub rozpusten po sestupu kvuli neprovozuschopnosti ZS) -&gt; HC Teplice Huskies (2018+ novy mladeznicky klub, novy zimni stadion otevren 2019). city Teplice. POZOR: Teplice nad Metují = JINE MESTO (Královehradecky kraj, Slavoj Teplice nL Metují) - separate od stredoceskych Teplic. || Teplice = HC Stadion Teplice (1945-2007) -&gt; HC Teplice Huskies (2019-dnes) (Pavlovo upresneni 04/2026 + Wiki + FK Teplice paralelni vyvoj). Genealogie podle paralelni fotbalove linie: 1945 zalozeni -&gt; 1948 Sokol -&gt; 1949 Technomat (podnik OD - obchodni dum) -&gt; 1951 Vodotechna (vodni stavby) -&gt; 1952 Ingstav (inzenyrska stavba) -&gt; 1953 Tatran Teplice (DSO reforma) -&gt; 1960 Slovan -&gt; 1966 Sklo Union -&gt; po 1991 menici se nazvy -&gt; 2007 PRERUSENI provozu - nositel hokejove tradice mesta pokracuje v Teplice Huskies (2019) -&gt; 2010 zbytky presun do Biliny -&gt; 2019 obnoveni HC Teplice Huskies (novy ZS). Patterns: Technomat Teplice, Vodotechna, Tatran Teplice, Slovan Teplice. Plus mensi paralelni kluby v 50. letech: Sokol Testroj/Somet/Ingstav, Sokol Sklarny Retenice, Jiskra Retenice (1955 sloucena s Tatranem), Spartak Trnovany, Banik Teplice, Lokomotiva Teplice, Tatran Sobedruhy. Retenice + Trnovany + Sobedruhy = mestske casti Teplic (Retenice oficialne od 1963). Sklarny Retenice = city Teplice. || Teplice (Wiki D42 - registr ustavy 04/2026). Hlavni chain HC Stadion Teplice (1945-2007) -&gt; Teplice Huskies (2019-): Technomat -&gt; Vodotechna -&gt; Ingstav -&gt; Tatran (1953) -&gt; Slovan (1960) -&gt; Sklo Union (1966). Plus mestske casti: Retenice (sklarny od 1890), Trnovany, Sobedruhy. city Teplice. || TBD: city 'Teplice' → 'Stadion Litoměřice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Oprava city: „Testroj Teplice" → „Teplice" (Testroj = závod). || Sokol Testroj Teplice 52/53 - hlavni klub (Testroj podnik). Teplice = HC Stadion Teplice (Wiki D42 - registr 04/2026). Genealogie: Technomat Teplice (49/50, podnik Technomat) -&gt; Sokol Testroj Teplice (52/53, Testroj/Somet podnik) -&gt; Tatran Teplice (53/54+ DSO reforma). Plus Sklarny Retenice paralelni klub (skladlo se 55/56 s Tatranem Teplice). Dnesni klub HC Stadion Teplice. Patterns: Technomat Teplice, Sokol Testroj, Tatran Teplice, Sklárny Řetenice. city Teplice. || Sokol Testroj Teplice 52/53 (20_Ústecký okresni). Testroj = podnik (puvodne Technomat). Teplice = HC Stadion Teplice / HC Teplice Huskies (Wiki D42 + hokej.cz - 04/2026). Genealogie: Klub zalozen 1945. Technomat Teplice (1949-50, podnikovy klub Technomat) -&gt; Sokol Testroj (1952) -&gt; Tatran Teplice (1953+, DSO reforma) -&gt;... -&gt; HC Stadion Teplice (do 2007, klub rozpusten po sestupu kvuli neprovozuschopnosti ZS) -&gt; HC Teplice Huskies (2018+ novy mladeznicky klub, novy zimni stadion otevren 2019). city Teplice. POZOR: Teplice nad Metují = JINE MESTO (Královehradecky kraj, Slavoj Teplice nL Metují) - separate od stredoceskych Teplic. || Teplice = HC Stadion Teplice (1945-2007) -&gt; HC Teplice Huskies (2019-dnes) (Pavlovo upresneni 04/2026 + Wiki + FK Teplice paralelni vyvoj). Genealogie podle paralelni fotbalove linie: 1945 zalozeni -&gt; 1948 Sokol -&gt; 1949 Technomat (podnik OD - obchodni dum) -&gt; 1951 Vodotechna (vodni stavby) -&gt; 1952 Ingstav (inzenyrska stavba) -&gt; 1953 Tatran Teplice (DSO reforma) -&gt; 1960 Slovan -&gt; 1966 Sklo Union -&gt; po 1991 menici se nazvy -&gt; 2007 PRERUSENI provozu - nositel hokejove tradice mesta pokracuje v Teplice Huskies (2019) -&gt; 2010 zbytky presun do Biliny -&gt; 2019 obnoveni HC Teplice Huskies (novy ZS). Patterns: Technomat Teplice, Vodotechna, Tatran Teplice, Slovan Teplice. Plus mensi paralelni kluby v 50. letech: Sokol Testroj/Somet/Ingstav, Sokol Sklarny Retenice, Jiskra Retenice (1955 sloucena s Tatranem), Spartak Trnovany, Banik Teplice, Lokomotiva Teplice, Tatran Sobedruhy. Retenice + Trnovany + Sobedruhy = mestske casti Teplic (Retenice oficialne od 1963). Sklarny Retenice = city Teplice. || Teplice (Wiki D42 - registr ustavy 04/2026). Hlavni chain HC Stadion Teplice (1945-2007) -&gt; Teplice Huskies (2019-): Technomat -&gt; Vodotechna -&gt; Ingstav -&gt; Tatran (1953) -&gt; Slovan (1960) -&gt; Sklo Union (1966). Plus mestske casti: Retenice (sklarny od 1890), Trnovany, Sobedruhy. city Teplice.</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>Stadion Litoměřice</t>
+          <t>Teplice</t>
         </is>
       </c>
     </row>
@@ -23712,12 +23894,12 @@
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov. || TBD: city 'Prostějov' → 'Nový Bydžov' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov.</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>Nový Bydžov</t>
+          <t>Prostějov</t>
         </is>
       </c>
     </row>
@@ -24238,12 +24420,12 @@
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>Jiskra Havlíčkův Brod = HC Rebel HB (Wiki D42 - registr ustavy 04/2026). city Havlíčkův Brod. || TBD: city 'Havlíčkův Brod' → 'Uherské Hradiště' (odvozeno z názvu klubu) [polish_almanach] || TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
+          <t>Jiskra Havlíčkův Brod = HC Rebel HB (Wiki D42 - registr ustavy 04/2026). city Havlíčkův Brod. || TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>Uherské Hradiště</t>
+          <t>Havlíčkův Brod</t>
         </is>
       </c>
     </row>
@@ -27635,7 +27817,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -27709,12 +27891,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CLUB_S2002_03_0006</t>
+          <t>CLUB_S2002_03_0017</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -27729,12 +27911,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CLUB_S2002_03_0017</t>
+          <t>CLUB_S2002_03_0024</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -27749,12 +27931,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CLUB_S2002_03_0018</t>
+          <t>CLUB_S2002_03_0055</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -27769,12 +27951,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CLUB_S2002_03_0023</t>
+          <t>CLUB_S2002_03_0063</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'České Budějovice' → 'Slezan Opava' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'HK Lev Slaný' → 'Slaný' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -27789,12 +27971,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CLUB_S2002_03_0024</t>
+          <t>CLUB_S2002_03_0065</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
         </is>
       </c>
     </row>
@@ -27809,12 +27991,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>CLUB_S2002_03_0027</t>
+          <t>CLUB_S2002_03_0067</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -27829,12 +28011,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CLUB_S2002_03_0055</t>
+          <t>CLUB_S2002_03_0069</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Vlci Jablonec nad Nisou' → 'Jablonec nad Nisou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -27849,12 +28031,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CLUB_S2002_03_0063</t>
+          <t>CLUB_S2002_03_0073</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'HK Lev Slaný' → 'Slaný' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'NED Hockey Nymburk' → 'Nymburk' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -27869,12 +28051,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>CLUB_S2002_03_0065</t>
+          <t>CLUB_S2002_03_0101</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+          <t>TBD: city 'VHS HC Benešov' → 'Benešov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -27889,12 +28071,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CLUB_S2002_03_0067</t>
+          <t>CLUB_S2002_03_0116</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -27909,12 +28091,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CLUB_S2002_03_0069</t>
+          <t>CLUB_S2002_03_0127</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'Vlci Jablonec nad Nisou' → 'Jablonec nad Nisou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -27929,12 +28111,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>CLUB_S2002_03_0073</t>
+          <t>CLUB_S2002_03_0149</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'NED Hockey Nymburk' → 'Nymburk' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
         </is>
       </c>
     </row>
@@ -27949,12 +28131,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>CLUB_S2002_03_0101</t>
+          <t>CLUB_S2002_03_0160</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'VHS HC Benešov' → 'Benešov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
         </is>
       </c>
     </row>
@@ -27969,12 +28151,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>CLUB_S2002_03_0116</t>
+          <t>CLUB_S2002_03_0164</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
         </is>
       </c>
     </row>
@@ -27989,12 +28171,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>CLUB_S2002_03_0116</t>
+          <t>CLUB_S2002_03_0176</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
         </is>
       </c>
     </row>
@@ -28009,12 +28191,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>CLUB_S2002_03_0119</t>
+          <t>CLUB_S2002_03_0179</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -28029,12 +28211,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>CLUB_S2002_03_0126</t>
+          <t>CLUB_S2002_03_0184</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'Teplice' → 'Stadion Litoměřice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -28049,12 +28231,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CLUB_S2002_03_0127</t>
+          <t>CLUB_S2002_03_0186</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -28069,12 +28251,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CLUB_S2002_03_0149</t>
+          <t>CLUB_S2002_03_0188</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
         </is>
       </c>
     </row>
@@ -28089,197 +28271,17 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>CLUB_S2002_03_0160</t>
+          <t>CLUB_S2002_03_0193</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>22</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>CLUB_S2002_03_0164</t>
-        </is>
-      </c>
-      <c r="D23" s="5" t="inlineStr">
-        <is>
-          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>23</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>CLUB_S2002_03_0171</t>
-        </is>
-      </c>
-      <c r="D24" s="5" t="inlineStr">
-        <is>
-          <t>TBD: city 'Prostějov' → 'Nový Bydžov' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>24</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>CLUB_S2002_03_0176</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="inlineStr">
-        <is>
-          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>25</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>CLUB_S2002_03_0179</t>
-        </is>
-      </c>
-      <c r="D26" s="5" t="inlineStr">
-        <is>
-          <t>TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>26</v>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>CLUB_S2002_03_0184</t>
-        </is>
-      </c>
-      <c r="D27" s="5" t="inlineStr">
-        <is>
-          <t>TBD: city 'Havlíčkův Brod' → 'Uherské Hradiště' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>27</v>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>CLUB_S2002_03_0184</t>
-        </is>
-      </c>
-      <c r="D28" s="5" t="inlineStr">
-        <is>
-          <t>TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>28</v>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>CLUB_S2002_03_0186</t>
-        </is>
-      </c>
-      <c r="D29" s="5" t="inlineStr">
-        <is>
-          <t>TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>29</v>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>CLUB_S2002_03_0188</t>
-        </is>
-      </c>
-      <c r="D30" s="5" t="inlineStr">
-        <is>
-          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>30</v>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>CLUB_S2002_03_0193</t>
-        </is>
-      </c>
-      <c r="D31" s="5" t="inlineStr">
-        <is>
           <t>TBD: city 'VSK Technika Brno' → 'Technika Brno' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F31"/>
+  <autoFilter ref="A1:F22"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/S2002_03_FINAL.xlsx
+++ b/data/S2002_03_FINAL.xlsx
@@ -10467,7 +10467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L84"/>
+  <dimension ref="A1:N84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10531,6 +10531,16 @@
           <t>prev_node_id</t>
         </is>
       </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>entry</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>phase_order</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -13695,8 +13705,6 @@
         </is>
       </c>
     </row>
-    <row r="71"/>
-    <row r="72"/>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
@@ -13826,7 +13834,6 @@
         </is>
       </c>
     </row>
-    <row r="80"/>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>

--- a/data/S2002_03_FINAL.xlsx
+++ b/data/S2002_03_FINAL.xlsx
@@ -10719,6 +10719,16 @@
           <t>NODE_S2002_03_0001</t>
         </is>
       </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0010</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0016</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -10733,6 +10743,14 @@
         <is>
           <t>NODE_S2001_02_0004</t>
         </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>14 týmů</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -10907,6 +10925,16 @@
           <t>NODE_S2002_03_0007</t>
         </is>
       </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0010</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0019</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -10921,6 +10949,14 @@
         <is>
           <t>NODE_S2001_02_0008</t>
         </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>horní část ZČ</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -11001,6 +11037,16 @@
           <t>NODE_S2002_03_0007</t>
         </is>
       </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0011</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0019</t>
+        </is>
+      </c>
       <c r="I11" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -11015,6 +11061,14 @@
         <is>
           <t>NODE_S2001_02_0010</t>
         </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>horní polovina ZČ</t>
+        </is>
+      </c>
+      <c r="N11" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -11048,6 +11102,16 @@
           <t>NODE_S2002_03_0007</t>
         </is>
       </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0015</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0014</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -11062,6 +11126,14 @@
         <is>
           <t>NODE_S2001_02_0011</t>
         </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N12" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="13">
@@ -11095,6 +11167,8 @@
           <t>NODE_S2002_03_0007</t>
         </is>
       </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -11109,6 +11183,14 @@
         <is>
           <t>NODE_S2001_02_0012</t>
         </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>sk. o 5.–8. (dolní)</t>
+        </is>
+      </c>
+      <c r="N13" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="14">
@@ -11142,6 +11224,8 @@
           <t>NODE_S2002_03_0007</t>
         </is>
       </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -11156,6 +11240,14 @@
         <is>
           <t>NODE_S2001_02_0013</t>
         </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>sk. o 5.–8. (horní)</t>
+        </is>
+      </c>
+      <c r="N14" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="15">
@@ -11189,6 +11281,8 @@
           <t>NODE_S2002_03_0007</t>
         </is>
       </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -11203,6 +11297,14 @@
         <is>
           <t>NODE_S2001_02_0014</t>
         </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>poražení SF</t>
+        </is>
+      </c>
+      <c r="N15" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="16">
@@ -11236,6 +11338,8 @@
           <t>NODE_S2002_03_0007</t>
         </is>
       </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -11250,6 +11354,14 @@
         <is>
           <t>NODE_S2001_02_0015</t>
         </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N16" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="17">
@@ -11283,6 +11395,8 @@
           <t>NODE_S2002_03_0001</t>
         </is>
       </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -11297,6 +11411,14 @@
         <is>
           <t>NODE_S2001_02_0016</t>
         </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N17" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -11330,6 +11452,8 @@
           <t>NODE_S2002_03_0007</t>
         </is>
       </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -11344,6 +11468,14 @@
         <is>
           <t>NODE_S2001_02_0017</t>
         </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>poražení play-off</t>
+        </is>
+      </c>
+      <c r="N18" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="19">
@@ -11377,6 +11509,8 @@
           <t>NODE_S2002_03_0007</t>
         </is>
       </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -11391,6 +11525,14 @@
         <is>
           <t>NODE_S2001_02_0018</t>
         </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>o 9. místo</t>
+        </is>
+      </c>
+      <c r="N19" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -11424,6 +11566,16 @@
           <t>NODE_S2002_03_0007</t>
         </is>
       </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0013</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0012</t>
+        </is>
+      </c>
       <c r="I20" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -11438,6 +11590,14 @@
         <is>
           <t>NODE_S2001_02_0019</t>
         </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>poražení ČF</t>
+        </is>
+      </c>
+      <c r="N20" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="21">
@@ -11565,6 +11725,16 @@
           <t>NODE_S2002_03_0003</t>
         </is>
       </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0023</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0027</t>
+        </is>
+      </c>
       <c r="I23" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -11579,6 +11749,14 @@
         <is>
           <t>NODE_S2001_02_0022</t>
         </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>14 týmů</t>
+        </is>
+      </c>
+      <c r="N23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -11612,6 +11790,16 @@
           <t>NODE_S2002_03_0003</t>
         </is>
       </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0024</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0027</t>
+        </is>
+      </c>
       <c r="I24" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -11626,6 +11814,14 @@
         <is>
           <t>NODE_S2001_02_0023</t>
         </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>střed tabulky ZČ</t>
+        </is>
+      </c>
+      <c r="N24" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -11659,6 +11855,12 @@
           <t>NODE_S2002_03_0003</t>
         </is>
       </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0025</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -11673,6 +11875,14 @@
         <is>
           <t>NODE_S2001_02_0024</t>
         </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>horní ZČ + postupující z předkola</t>
+        </is>
+      </c>
+      <c r="N25" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="26">
@@ -11706,6 +11916,12 @@
           <t>NODE_S2002_03_0003</t>
         </is>
       </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0026</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -11720,6 +11936,14 @@
         <is>
           <t>NODE_S2001_02_0025</t>
         </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N26" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="27">
@@ -11753,6 +11977,8 @@
           <t>NODE_S2002_03_0003</t>
         </is>
       </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -11767,6 +11993,14 @@
         <is>
           <t>NODE_S2001_02_0026</t>
         </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N27" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="28">
@@ -11800,6 +12034,8 @@
           <t>NODE_S2002_03_0003</t>
         </is>
       </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -11814,6 +12050,14 @@
         <is>
           <t>NODE_S2001_02_0027</t>
         </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>6.–14. ZČ</t>
+        </is>
+      </c>
+      <c r="N28" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -12077,6 +12321,8 @@
           <t>NODE_S2002_03_0032</t>
         </is>
       </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -12091,6 +12337,14 @@
         <is>
           <t>NODE_S2001_02_0038</t>
         </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>8 týmů</t>
+        </is>
+      </c>
+      <c r="N34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -12171,6 +12425,8 @@
           <t>NODE_S2002_03_0032</t>
         </is>
       </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -12180,6 +12436,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>poražení ČF</t>
+        </is>
+      </c>
+      <c r="N36" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="37">
@@ -12354,6 +12618,12 @@
           <t>NODE_S2002_03_0036</t>
         </is>
       </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0040</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -12368,6 +12638,14 @@
         <is>
           <t>NODE_S2001_02_0044</t>
         </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>horní polovina ZČ</t>
+        </is>
+      </c>
+      <c r="N40" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="41">
@@ -12401,6 +12679,12 @@
           <t>NODE_S2002_03_0036</t>
         </is>
       </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0041</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -12415,6 +12699,14 @@
         <is>
           <t>NODE_S2001_02_0045</t>
         </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N41" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="42">
@@ -12448,6 +12740,8 @@
           <t>NODE_S2002_03_0036</t>
         </is>
       </c>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -12462,6 +12756,14 @@
         <is>
           <t>NODE_S2001_02_0046</t>
         </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N42" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="43">
@@ -12589,6 +12891,8 @@
           <t>NODE_S2002_03_0036</t>
         </is>
       </c>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -12603,6 +12907,14 @@
         <is>
           <t>NODE_S2001_02_0049</t>
         </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N45" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="46">
@@ -12720,6 +13032,12 @@
           <t>NODE_S2002_03_0036</t>
         </is>
       </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0039</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -12734,6 +13052,14 @@
         <is>
           <t>NODE_S2001_02_0051</t>
         </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>horní část ZČ</t>
+        </is>
+      </c>
+      <c r="N48" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="49">
@@ -12861,6 +13187,12 @@
           <t>NODE_S2002_03_0049</t>
         </is>
       </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0051</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -12875,6 +13207,14 @@
         <is>
           <t>NODE_S2001_02_0058</t>
         </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>10 týmů</t>
+        </is>
+      </c>
+      <c r="N51" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -12908,6 +13248,8 @@
           <t>NODE_S2002_03_0049</t>
         </is>
       </c>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -12922,6 +13264,14 @@
         <is>
           <t>NODE_S2001_02_0061</t>
         </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N52" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="53">
@@ -13254,6 +13604,8 @@
           <t>NODE_S2002_03_0056</t>
         </is>
       </c>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13263,6 +13615,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N60" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="61">
@@ -13296,6 +13656,8 @@
           <t>NODE_S2002_03_0056</t>
         </is>
       </c>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13310,6 +13672,14 @@
         <is>
           <t>NODE_S2001_02_0077</t>
         </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N61" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="62">
@@ -13385,6 +13755,12 @@
           <t>NODE_S2002_03_0061</t>
         </is>
       </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0063</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13394,6 +13770,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>9 týmů</t>
+        </is>
+      </c>
+      <c r="N63" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -13427,6 +13811,8 @@
           <t>NODE_S2002_03_0061</t>
         </is>
       </c>
+      <c r="G64" t="inlineStr"/>
+      <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13436,6 +13822,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N64" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="65">
@@ -13511,6 +13905,12 @@
           <t>NODE_S2002_03_0064</t>
         </is>
       </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0066</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13520,6 +13920,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>9 týmů</t>
+        </is>
+      </c>
+      <c r="N66" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -13553,6 +13961,8 @@
           <t>NODE_S2002_03_0064</t>
         </is>
       </c>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13562,6 +13972,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N67" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="68">
@@ -13642,6 +14060,12 @@
           <t>NODE_S2002_03_0067</t>
         </is>
       </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0069</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13656,6 +14080,14 @@
         <is>
           <t>NODE_S2001_02_0086</t>
         </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>6 týmů</t>
+        </is>
+      </c>
+      <c r="N69" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="70">
@@ -13689,6 +14121,8 @@
           <t>NODE_S2002_03_0067</t>
         </is>
       </c>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13704,7 +14138,17 @@
           <t>NODE_S2001_02_0087</t>
         </is>
       </c>
-    </row>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N70" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="71"/>
+    <row r="72"/>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
@@ -13834,6 +14278,7 @@
         </is>
       </c>
     </row>
+    <row r="80"/>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>

--- a/data/S2002_03_FINAL.xlsx
+++ b/data/S2002_03_FINAL.xlsx
@@ -828,6 +828,11 @@
           <t>HC Slavia Praha (C)</t>
         </is>
       </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
       <c r="F6" t="n">
         <v>52</v>
       </c>
@@ -11167,8 +11172,6 @@
           <t>NODE_S2002_03_0007</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -11224,8 +11227,6 @@
           <t>NODE_S2002_03_0007</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -11281,8 +11282,6 @@
           <t>NODE_S2002_03_0007</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -11338,8 +11337,6 @@
           <t>NODE_S2002_03_0007</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -11395,8 +11392,6 @@
           <t>NODE_S2002_03_0001</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -11452,8 +11447,6 @@
           <t>NODE_S2002_03_0007</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -11509,8 +11502,6 @@
           <t>NODE_S2002_03_0007</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -11860,7 +11851,6 @@
           <t>NODE_S2002_03_0025</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -11921,7 +11911,6 @@
           <t>NODE_S2002_03_0026</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -11977,8 +11966,6 @@
           <t>NODE_S2002_03_0003</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -12034,8 +12021,6 @@
           <t>NODE_S2002_03_0003</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -12321,8 +12306,6 @@
           <t>NODE_S2002_03_0032</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -12425,8 +12408,6 @@
           <t>NODE_S2002_03_0032</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -12623,7 +12604,6 @@
           <t>NODE_S2002_03_0040</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -12684,7 +12664,6 @@
           <t>NODE_S2002_03_0041</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -12740,8 +12719,6 @@
           <t>NODE_S2002_03_0036</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -12891,8 +12868,6 @@
           <t>NODE_S2002_03_0036</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13037,7 +13012,6 @@
           <t>NODE_S2002_03_0039</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13192,7 +13166,6 @@
           <t>NODE_S2002_03_0051</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13248,8 +13221,6 @@
           <t>NODE_S2002_03_0049</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13604,8 +13575,6 @@
           <t>NODE_S2002_03_0056</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13656,8 +13625,6 @@
           <t>NODE_S2002_03_0056</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13760,7 +13727,6 @@
           <t>NODE_S2002_03_0063</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13811,8 +13777,6 @@
           <t>NODE_S2002_03_0061</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13910,7 +13874,6 @@
           <t>NODE_S2002_03_0066</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -13961,8 +13924,6 @@
           <t>NODE_S2002_03_0064</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr"/>
-      <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14065,7 +14026,6 @@
           <t>NODE_S2002_03_0069</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14121,8 +14081,6 @@
           <t>NODE_S2002_03_0067</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr"/>
-      <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -14147,8 +14105,6 @@
         <v>5</v>
       </c>
     </row>
-    <row r="71"/>
-    <row r="72"/>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
@@ -14278,7 +14234,6 @@
         </is>
       </c>
     </row>
-    <row r="80"/>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
@@ -28075,7 +28030,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28255,6 +28210,18 @@
       <c r="B15" t="inlineStr">
         <is>
           <t>0 oprav kvalifikačních levelů. Sloupec Q (level) aktualizován.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>mistr</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>HC Slavia Praha</t>
         </is>
       </c>
     </row>

--- a/data/S2002_03_FINAL.xlsx
+++ b/data/S2002_03_FINAL.xlsx
@@ -14105,6 +14105,8 @@
         <v>5</v>
       </c>
     </row>
+    <row r="71"/>
+    <row r="72"/>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
@@ -14234,6 +14236,7 @@
         </is>
       </c>
     </row>
+    <row r="80"/>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>

--- a/data/S2002_03_FINAL.xlsx
+++ b/data/S2002_03_FINAL.xlsx
@@ -3485,7 +3485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W50"/>
+  <dimension ref="A1:W89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -7234,6 +7234,1715 @@
       <c r="V50" t="inlineStr">
         <is>
           <t>TR_S2002_03_00205</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0072</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>1</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>HC Spartak Choceň B</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0072</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0244</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>TR_S2002_03_00277</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>2</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>TJ Sokol Žamberk</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0072</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0245</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>TR_S2002_03_00278</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>3</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>TJ Sokol Tisová</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0072</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0246</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>TR_S2002_03_00279</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>4</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>TJ Voděrady</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0072</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0247</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>TR_S2002_03_00280</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>5</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>HC Ústí nad Orlicí A</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0072</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0248</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>TR_S2002_03_00281</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>6</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>TJ Lanškroun</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0072</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0249</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>TR_S2002_03_00282</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>7</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>TJ Jiskra Králíky</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0072</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0250</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>TR_S2002_03_00283</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>8</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>TJ Sokol Řetová</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0072</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0251</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>TR_S2002_03_00284</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>9</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>TJ Semanín</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0072</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0252</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>TR_S2002_03_00285</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>10</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>TJ Sokol Verměřovice</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0072</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0253</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>TR_S2002_03_00286</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>11</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>TJ HC Dlouhoňovice</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0072</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0254</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>TR_S2002_03_00287</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>12</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>TJ Sokol Nekoř</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0072</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0255</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>TR_S2002_03_00288</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Brno Venkov</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0073</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>1</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>HC Rico Veverská Bítýška</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>Brno Venkov</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0073</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0256</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>TR_S2002_03_00289</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>2</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Sokol Malhostovice</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>Brno Venkov</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0073</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0257</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>TR_S2002_03_00290</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>3</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>TJ Šerkovice</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>Brno Venkov</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0073</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0258</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>TR_S2002_03_00291</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>4</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>HC Zastávka</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>Brno Venkov</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0073</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0259</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>TR_S2002_03_00292</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>5</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>HC Lachtani Brno</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>Brno Venkov</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0073</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0260</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>TR_S2002_03_00293</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>6</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>HC Draci Modřice</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>Brno Venkov</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0073</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0261</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>TR_S2002_03_00294</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>1</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Sokol Okříšky</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>Brno Venkov</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0073</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0262</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>TR_S2002_03_00295</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>1</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>SK Reinpo Žďár nad Sázavou</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>Brno Venkov</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0073</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0263</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>TR_S2002_03_00296</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>2</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>HC Granit Žďár nad Sázavou</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>Brno Venkov</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0073</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0264</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>TR_S2002_03_00297</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>3</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>HC Kozel Jámy</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>Brno Venkov</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0073</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0265</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>TR_S2002_03_00298</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>4</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>HC Vatín</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>Brno Venkov</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0073</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0266</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>TR_S2002_03_00299</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>5</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>TJ Slavkovice</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>Brno Venkov</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0073</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0267</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>TR_S2002_03_00300</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>6</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>TJ Jiskra Vír</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>Brno Venkov</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0073</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0268</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>TR_S2002_03_00301</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>7</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>TJ Řečice</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>Brno Venkov</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0073</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0269</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>TR_S2002_03_00302</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>1</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>HHK Gremis Velké Meziříčí</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>Brno Venkov</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0073</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0270</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>TR_S2002_03_00303</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>2</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Velká Bíteš</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>Brno Venkov</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0073</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0271</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>TR_S2002_03_00304</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>3</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>SK Mostiště</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>Brno Venkov</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0073</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0272</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>TR_S2002_03_00305</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>4</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Slavoj Polná</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>Brno Venkov</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0073</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0273</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>TR_S2002_03_00306</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>5</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>HC Florida Velké Meziříčí</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>Brno Venkov</t>
+        </is>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0073</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q83" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0274</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>TR_S2002_03_00307</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>6</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>TJ Jiskra Měřín</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>Brno Venkov</t>
+        </is>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0073</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q84" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0275</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>TR_S2002_03_00308</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>7</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>SK Netín</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>Brno Venkov</t>
+        </is>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0073</t>
+        </is>
+      </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q85" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0276</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>TR_S2002_03_00309</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>8</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>HC Sokol Křižanov</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>Brno Venkov</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0073</t>
+        </is>
+      </c>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q86" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0277</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>TR_S2002_03_00310</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>3</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Spartak Velká Bíteš B</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>Brno Venkov</t>
+        </is>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0073</t>
+        </is>
+      </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q87" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0278</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>TR_S2002_03_00311</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>4</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>HHK B Gremis Velké Meziříčí</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>Brno Venkov</t>
+        </is>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0073</t>
+        </is>
+      </c>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q88" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0279</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>TR_S2002_03_00312</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>6</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>TJ Slavoj Polná</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>Brno Venkov</t>
+        </is>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0073</t>
+        </is>
+      </c>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q89" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0280</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>TR_S2002_03_00313</t>
         </is>
       </c>
     </row>
@@ -9187,7 +10896,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W14"/>
+  <dimension ref="A1:W29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -10151,6 +11860,668 @@
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Opava</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0074</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Slavia Malé Hoštice</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Opava</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0074</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0281</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>TR_S2002_03_00314</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>2</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>HC Slezan Old Boys</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Opava</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0074</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0282</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>TR_S2002_03_00315</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>3</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>SK Městská policie Opava</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Opava</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0074</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0283</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>TR_S2002_03_00316</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>4</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>HC Buly Centrum Kravaře</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Opava</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0074</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0284</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>TR_S2002_03_00317</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>5</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>HC Oceán Opava</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Opava</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0074</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0285</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>TR_S2002_03_00318</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>6</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>HC 001 Opava</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Opava</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0074</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0286</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>TR_S2002_03_00319</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>7</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>SKP Opava</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Opava</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0074</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0287</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>TR_S2002_03_00320</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>SK Kravaře</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Opava</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0074</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0288</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>TR_S2002_03_00321</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>2</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>HC Tygři Opava</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Opava</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0074</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0289</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>TR_S2002_03_00322</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>3</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>HC Torpédo Služovice</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>Opava</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0074</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0290</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>TR_S2002_03_00323</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>4</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>HC Kozel Těškovice</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Opava</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0074</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0291</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>TR_S2002_03_00324</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>5</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>SK HC Prajz Hlučín</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>Opava</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0074</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0292</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>TR_S2002_03_00325</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>6</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Slavia Malé Hoštice B</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>Opava</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0074</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0293</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>TR_S2002_03_00326</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>7</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>HC Býci Opava</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>Opava</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0074</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0294</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>TR_S2002_03_00327</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10472,7 +12843,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N84"/>
+  <dimension ref="A1:N89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14262,6 +16633,191 @@
       <c r="A84" t="inlineStr">
         <is>
           <t>II.liga: Západ/Střed/Východ + 8F/QF/SF/finále. Nové kraje.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0070</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Středočeský – Kutná Hora</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>league</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>REG_STC</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0048</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy).</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0071</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Jihočeský – České Budějovice a Český Krumlov</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>league</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>REG_JHC</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0049</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy).</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0072</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Východočeský – Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>league</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>REG_VYC</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0056</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy).</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0073</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Jihomoravský-Vysočina – Brno Venkov</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>league</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>REG_VYC</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0056</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy).</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0074</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Severomoravský – Opava</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>league</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>REG_SVM</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0067</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy).</t>
         </is>
       </c>
     </row>
@@ -17297,7 +19853,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J196"/>
+  <dimension ref="A1:J286"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="10" max="10"/>
@@ -25562,6 +28118,2906 @@
       <c r="J196" t="inlineStr">
         <is>
           <t>Studénka</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0205</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Stadion Kutná Hora B</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Stadion Kutná Hora B</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>30STRC</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0206</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Slavia Vinaře</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Slavia Vinaře</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>30STRC</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0207</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Sokol Uhl.Janovice</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Sokol Uhl.Janovice</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>30STRC</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0208</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Slavoj Čáslav</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Slavoj Čáslav</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>30STRC</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0209</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Sokol Řendějov</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Sokol Řendějov</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>30STRC</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0210</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Jiskra Zruč nad Sázavou</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Jiskra Zruč nad Sázavou</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>30STRC</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0211</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>HC Kladno 1988 „B“</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>HC Kladno 1988 „B“</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>30STRC</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0212</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>HC Lány</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>HC Lány</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>30STRC</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0213</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Sokol ČNES Braškov</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Sokol ČNES Braškov</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>30STRC</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0214</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Sokol Hnidousy- Motyčín</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Sokol Hnidousy- Motyčín</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>30STRC</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0215</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Ford VM Kladno</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Ford VM Kladno</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>30STRC</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0216</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>HK Kralupy nad Vltavou „B“</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>HK Kralupy nad Vltavou „B“</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>30STRC</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0217</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Důl Kladno</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Důl Kladno</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>30STRC</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0218</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>HC Zlonice „B“</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>HC Zlonice „B“</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>30STRC</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0219</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>finále</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>finále</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>30STRC</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0220</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>SD-CHO 6:6,4:6</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>SD-CHO 6:6,4:6</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>30STRC</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0221</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>finále: Dvůr-Týniště 7:2</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>finále: Dvůr-Týniště 7:2</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>30STRC</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0222</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Cannons Hluboká</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Cannons Hluboká</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>30JHCK</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0223</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Slavoj Český Krumlov B</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Slavoj Český Krumlov B</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>30JHCK</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0224</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Cheyennes České Budějovice</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Cheyennes České Budějovice</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>30JHCK</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0225</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Sharks Český Krumlov</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Sharks Český Krumlov</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>30JHCK</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0226</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Aspera České Budějovice</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>Aspera České Budějovice</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>30JHCK</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0227</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Barons Hluboká</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>Barons Hluboká</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>30JHCK</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0228</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Petříkov</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>Petříkov</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>30JHCK</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0229</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Netolice</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>Netolice</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>30JHCK</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0230</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>Spartak Kaplice</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>Spartak Kaplice</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>30JHCK</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0231</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>Přísečná</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>Přísečná</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>30JHCK</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0232</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>Velešín</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>Velešín</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>30JHCK</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0233</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>HoDO České Budějovice</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>HoDO České Budějovice</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>30JHCK</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0234</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>B-Praktik Český Krumlov</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>B-Praktik Český Krumlov</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>30JHCK</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0235</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>Slavoj Český Krumlov dorost</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>Slavoj Český Krumlov dorost</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>30JHCK</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0236</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>Pluhův Žďár</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>Pluhův Žďár</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>30JHCK</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0237</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>Policie</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>Policie</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>30JHCK</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0238</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>Fruko</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>Fruko</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>30JHCK</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0239</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>Obal</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>Obal</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>30JHCK</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0240</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>Nová Včelnice</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>Nová Včelnice</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>30JHCK</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0241</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>Hříbek</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>Hříbek</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>30JHCK</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0242</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>Jitka</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>Jitka</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>30JHCK</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0243</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>První Kamenická</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>První Kamenická</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>30JHCK</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0244</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>HC Spartak Choceň B</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>HC Spartak Choceň B</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>30VYCH</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0245</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>TJ Sokol Žamberk</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>TJ Sokol Žamberk</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>30VYCH</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0246</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>TJ Sokol Tisová</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>TJ Sokol Tisová</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>30VYCH</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0247</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>TJ Voděrady</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>TJ Voděrady</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>30VYCH</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0248</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>HC Ústí nad Orlicí A</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>HC Ústí nad Orlicí A</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>30VYCH</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0249</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>TJ Lanškroun</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>TJ Lanškroun</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>30VYCH</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I241" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0250</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>TJ Jiskra Králíky</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>TJ Jiskra Králíky</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>30VYCH</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I242" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0251</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>TJ Sokol Řetová</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>TJ Sokol Řetová</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>30VYCH</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I243" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0252</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>TJ Semanín</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>TJ Semanín</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>30VYCH</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I244" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0253</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>TJ Sokol Verměřovice</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>TJ Sokol Verměřovice</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>30VYCH</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I245" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0254</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>TJ HC Dlouhoňovice</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>TJ HC Dlouhoňovice</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>30VYCH</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0255</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>TJ Sokol Nekoř</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>TJ Sokol Nekoř</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>30VYCH</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0256</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>HC Rico Veverská Bítýška</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>HC Rico Veverská Bítýška</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>30VYCH</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I248" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0257</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>Sokol Malhostovice</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>Sokol Malhostovice</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>30VYCH</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I249" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0258</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>TJ Šerkovice</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>TJ Šerkovice</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>30VYCH</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I250" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0259</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>HC Zastávka</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>HC Zastávka</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>30VYCH</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I251" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0260</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>HC Lachtani Brno</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>HC Lachtani Brno</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>30VYCH</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I252" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0261</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>HC Draci Modřice</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>HC Draci Modřice</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>30VYCH</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I253" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0262</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>Sokol Okříšky</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>Sokol Okříšky</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>30VYCH</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I254" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0263</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>SK Reinpo Žďár nad Sázavou</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>SK Reinpo Žďár nad Sázavou</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>30VYCH</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I255" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0264</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>HC Granit Žďár nad Sázavou</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>HC Granit Žďár nad Sázavou</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>30VYCH</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I256" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0265</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>HC Kozel Jámy</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>HC Kozel Jámy</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>30VYCH</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I257" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0266</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>HC Vatín</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>HC Vatín</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>30VYCH</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I258" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0267</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>TJ Slavkovice</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>TJ Slavkovice</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>30VYCH</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I259" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0268</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>TJ Jiskra Vír</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>TJ Jiskra Vír</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>30VYCH</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I260" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0269</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>TJ Řečice</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>TJ Řečice</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>30VYCH</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I261" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0270</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>HHK Gremis Velké Meziříčí</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>HHK Gremis Velké Meziříčí</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>30VYCH</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I262" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0271</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>Velká Bíteš</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>Velká Bíteš</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>30VYCH</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I263" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0272</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>SK Mostiště</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>SK Mostiště</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>30VYCH</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I264" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0273</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>Slavoj Polná</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>Slavoj Polná</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>30VYCH</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I265" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0274</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>HC Florida Velké Meziříčí</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>HC Florida Velké Meziříčí</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>30VYCH</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I266" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0275</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>TJ Jiskra Měřín</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>TJ Jiskra Měřín</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>30VYCH</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I267" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0276</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>SK Netín</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>SK Netín</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>30VYCH</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I268" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0277</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>HC Sokol Křižanov</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>HC Sokol Křižanov</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>30VYCH</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I269" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0278</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>Spartak Velká Bíteš B</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>Spartak Velká Bíteš B</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>30VYCH</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I270" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0279</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>HHK B Gremis Velké Meziříčí</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>HHK B Gremis Velké Meziříčí</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>30VYCH</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I271" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0280</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>TJ Slavoj Polná</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>TJ Slavoj Polná</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>30VYCH</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I272" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0281</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>Slavia Malé Hoštice</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>Slavia Malé Hoštice</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>30SVMR</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I273" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0282</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>HC Slezan Old Boys</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>HC Slezan Old Boys</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>30SVMR</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I274" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0283</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>SK Městská policie Opava</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>SK Městská policie Opava</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>30SVMR</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I275" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0284</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>HC Buly Centrum Kravaře</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>HC Buly Centrum Kravaře</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>30SVMR</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I276" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0285</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>HC Oceán Opava</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>HC Oceán Opava</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>30SVMR</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I277" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0286</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>HC 001 Opava</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>HC 001 Opava</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>30SVMR</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I278" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0287</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>SKP Opava</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>SKP Opava</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>30SVMR</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I279" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0288</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>SK Kravaře</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>SK Kravaře</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>30SVMR</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I280" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0289</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>HC Tygři Opava</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>HC Tygři Opava</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>30SVMR</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I281" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0290</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>HC Torpédo Služovice</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>HC Torpédo Služovice</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>30SVMR</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I282" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0291</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>HC Kozel Těškovice</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>HC Kozel Těškovice</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>30SVMR</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I283" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0292</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>SK HC Prajz Hlučín</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>SK HC Prajz Hlučín</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>30SVMR</t>
+        </is>
+      </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I284" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0293</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>Slavia Malé Hoštice B</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>Slavia Malé Hoštice B</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>30SVMR</t>
+        </is>
+      </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I285" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0294</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>HC Býci Opava</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>HC Býci Opava</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>30SVMR</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I286" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
         </is>
       </c>
     </row>
@@ -36030,7 +41486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W26"/>
+  <dimension ref="A1:W44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -38072,6 +43528,784 @@
         </is>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Kutná Hora</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0070</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Stadion Kutná Hora B</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>Kutná Hora</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0070</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0205</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>TR_S2002_03_00238</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>2</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Slavia Vinaře</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>Kutná Hora</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0070</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0206</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>TR_S2002_03_00239</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>3</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Sokol Uhl.Janovice</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>Kutná Hora</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0070</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0207</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>TR_S2002_03_00240</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>4</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Slavoj Čáslav</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>Kutná Hora</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0070</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0208</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>TR_S2002_03_00241</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>5</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Sokol Řendějov</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>Kutná Hora</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0070</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0209</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>TR_S2002_03_00242</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>6</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Jiskra Zruč nad Sázavou</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>Kutná Hora</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0070</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0210</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>TR_S2002_03_00243</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>1</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>HC Kladno 1988 „B“</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>Kutná Hora</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0070</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0211</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>TR_S2002_03_00244</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>2</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>HC Lány</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>Kutná Hora</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0070</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0212</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>TR_S2002_03_00245</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>3</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Sokol ČNES Braškov</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>Kutná Hora</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0070</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0213</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>TR_S2002_03_00246</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>4</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Sokol Hnidousy- Motyčín</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>Kutná Hora</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0070</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0214</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>TR_S2002_03_00247</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>5</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Ford VM Kladno</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>Kutná Hora</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0070</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0215</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>TR_S2002_03_00248</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>6</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>HK Kralupy nad Vltavou „B“</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>Kutná Hora</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0070</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0216</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>TR_S2002_03_00249</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>7</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Důl Kladno</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>Kutná Hora</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0070</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0217</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>TR_S2002_03_00250</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>8</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>HC Zlonice „B“</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>Kutná Hora</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0070</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0218</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>TR_S2002_03_00251</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>finále</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>Kutná Hora</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0070</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0219</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>TR_S2002_03_00252</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>SD-CHO 6:6,4:6</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>Kutná Hora</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0070</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0220</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>TR_S2002_03_00253</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>finále: Dvůr-Týniště 7:2</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>Kutná Hora</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0070</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0221</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>TR_S2002_03_00254</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -38083,7 +44317,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W23"/>
+  <dimension ref="A1:W46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -39431,6 +45665,1028 @@
       <c r="V23" t="inlineStr">
         <is>
           <t>SER_S2002_03_0016</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>České Budějovice a Český Krumlov</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0071</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Cannons Hluboká</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>České Budějovice a Český Krumlov</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0071</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0222</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>TR_S2002_03_00255</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>2</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Slavoj Český Krumlov B</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>České Budějovice a Český Krumlov</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0071</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0223</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>TR_S2002_03_00256</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>3</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Cheyennes České Budějovice</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>České Budějovice a Český Krumlov</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0071</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0224</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>TR_S2002_03_00257</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>4</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Sharks Český Krumlov</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>České Budějovice a Český Krumlov</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0071</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0225</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>TR_S2002_03_00258</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>5</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Aspera České Budějovice</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>České Budějovice a Český Krumlov</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0071</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0226</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>TR_S2002_03_00259</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>6</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Barons Hluboká</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>České Budějovice a Český Krumlov</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0071</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0227</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>TR_S2002_03_00260</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>7</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Petříkov</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>České Budějovice a Český Krumlov</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0071</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0228</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>TR_S2002_03_00261</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>8</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Netolice</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>České Budějovice a Český Krumlov</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0071</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0229</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>TR_S2002_03_00262</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>9</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Spartak Kaplice</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>České Budějovice a Český Krumlov</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0071</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0230</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>TR_S2002_03_00263</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>10</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Přísečná</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>České Budějovice a Český Krumlov</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0071</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0231</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>TR_S2002_03_00264</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>11</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Velešín</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>České Budějovice a Český Krumlov</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0071</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0232</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>TR_S2002_03_00265</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>12</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>HoDO České Budějovice</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>České Budějovice a Český Krumlov</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0071</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0233</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>TR_S2002_03_00266</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>13</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>B-Praktik Český Krumlov</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>České Budějovice a Český Krumlov</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0071</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0234</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>TR_S2002_03_00267</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>14</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Slavoj Český Krumlov dorost</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>České Budějovice a Český Krumlov</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0071</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0235</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>TR_S2002_03_00268</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>1</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Pluhův Žďár</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>České Budějovice a Český Krumlov</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0071</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0236</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>TR_S2002_03_00269</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>2</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Policie</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>České Budějovice a Český Krumlov</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0071</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0237</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>TR_S2002_03_00270</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>3</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Fruko</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>České Budějovice a Český Krumlov</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0071</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0238</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>TR_S2002_03_00271</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>4</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Obal</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>České Budějovice a Český Krumlov</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0071</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0239</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>TR_S2002_03_00272</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>5</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Nová Včelnice</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>České Budějovice a Český Krumlov</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0071</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0240</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>TR_S2002_03_00273</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>6</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Hříbek</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>České Budějovice a Český Krumlov</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0071</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0241</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>TR_S2002_03_00274</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>7</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Jitka</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>České Budějovice a Český Krumlov</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0071</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0242</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>TR_S2002_03_00275</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>8</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>První Kamenická</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>České Budějovice a Český Krumlov</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0071</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>CLUB_S2002_03_0243</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>TR_S2002_03_00276</t>
         </is>
       </c>
     </row>

--- a/data/S2002_03_FINAL.xlsx
+++ b/data/S2002_03_FINAL.xlsx
@@ -39,7 +39,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -58,8 +58,12 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00B45309"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -81,6 +85,11 @@
         <fgColor rgb="00305496"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFE0B2"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -94,7 +103,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -105,6 +114,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -16476,8 +16487,6 @@
         <v>5</v>
       </c>
     </row>
-    <row r="71"/>
-    <row r="72"/>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
@@ -16607,7 +16616,6 @@
         </is>
       </c>
     </row>
-    <row r="80"/>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
@@ -33695,7 +33703,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -33752,7 +33760,7 @@
           <t>CLUB_S2002_03_0004</t>
         </is>
       </c>
-      <c r="D2" s="5" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -33772,7 +33780,7 @@
           <t>CLUB_S2002_03_0017</t>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -33792,7 +33800,7 @@
           <t>CLUB_S2002_03_0024</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -33812,7 +33820,7 @@
           <t>CLUB_S2002_03_0055</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
@@ -33832,7 +33840,7 @@
           <t>CLUB_S2002_03_0063</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>TBD: city 'HK Lev Slaný' → 'Slaný' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -33852,7 +33860,7 @@
           <t>CLUB_S2002_03_0065</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
         </is>
@@ -33872,7 +33880,7 @@
           <t>CLUB_S2002_03_0067</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -33892,7 +33900,7 @@
           <t>CLUB_S2002_03_0069</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>TBD: city 'Vlci Jablonec nad Nisou' → 'Jablonec nad Nisou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -33912,7 +33920,7 @@
           <t>CLUB_S2002_03_0073</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>TBD: city 'NED Hockey Nymburk' → 'Nymburk' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -33932,7 +33940,7 @@
           <t>CLUB_S2002_03_0101</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>TBD: city 'VHS HC Benešov' → 'Benešov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -33952,7 +33960,7 @@
           <t>CLUB_S2002_03_0116</t>
         </is>
       </c>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -33972,7 +33980,7 @@
           <t>CLUB_S2002_03_0127</t>
         </is>
       </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -33992,7 +34000,7 @@
           <t>CLUB_S2002_03_0149</t>
         </is>
       </c>
-      <c r="D14" s="5" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
         </is>
@@ -34012,7 +34020,7 @@
           <t>CLUB_S2002_03_0160</t>
         </is>
       </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
         </is>
@@ -34032,7 +34040,7 @@
           <t>CLUB_S2002_03_0164</t>
         </is>
       </c>
-      <c r="D16" s="5" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
         </is>
@@ -34052,7 +34060,7 @@
           <t>CLUB_S2002_03_0176</t>
         </is>
       </c>
-      <c r="D17" s="5" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
         </is>
@@ -34072,7 +34080,7 @@
           <t>CLUB_S2002_03_0179</t>
         </is>
       </c>
-      <c r="D18" s="5" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
         </is>
@@ -34092,7 +34100,7 @@
           <t>CLUB_S2002_03_0184</t>
         </is>
       </c>
-      <c r="D19" s="5" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
         </is>
@@ -34112,7 +34120,7 @@
           <t>CLUB_S2002_03_0186</t>
         </is>
       </c>
-      <c r="D20" s="5" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
         </is>
@@ -34132,7 +34140,7 @@
           <t>CLUB_S2002_03_0188</t>
         </is>
       </c>
-      <c r="D21" s="5" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
         </is>
@@ -34152,11 +34160,63 @@
           <t>CLUB_S2002_03_0193</t>
         </is>
       </c>
-      <c r="D22" s="5" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>TBD: city 'VSK Technika Brno' → 'Technika Brno' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>torzo</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>30_Zlínský L40 finále (Zlínský kraj) · NODE_S2002_03_0063</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>máme jen účastníky (TJ Valašské Meziříčí – HC Uherské Hradiště), chybí výsledek / odveta  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>torzo</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>30_Jihomoravský-Vysočina L40 finále · NODE_S2002_03_0066</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>máme jen účastníky (HC Nedvědice – HHK Velké Meziříčí), chybí výsledek / odveta  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+      <c r="F24" s="6" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:F22"/>

--- a/data/S2002_03_FINAL.xlsx
+++ b/data/S2002_03_FINAL.xlsx
@@ -103,7 +103,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -116,6 +116,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -12544,7 +12547,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12838,6 +12841,40 @@
         </is>
       </c>
       <c r="D23" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0063</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>[TBD] torzo: máme jen účastníky (TJ Valašské Meziříčí – HC Uherské Hradiště), chybí výsledek / odveta  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>NODE_S2002_03_0066</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>[TBD] torzo: máme jen účastníky (HC Nedvědice – HHK Velké Meziříčí), chybí výsledek / odveta  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
@@ -34180,7 +34217,7 @@
           <t>30_Zlínský L40 finále (Zlínský kraj) · NODE_S2002_03_0063</t>
         </is>
       </c>
-      <c r="D23" s="6" t="inlineStr">
+      <c r="D23" s="8" t="inlineStr">
         <is>
           <t>máme jen účastníky (TJ Valašské Meziříčí – HC Uherské Hradiště), chybí výsledek / odveta  [torzo-audit]</t>
         </is>
@@ -34206,7 +34243,7 @@
           <t>30_Jihomoravský-Vysočina L40 finále · NODE_S2002_03_0066</t>
         </is>
       </c>
-      <c r="D24" s="6" t="inlineStr">
+      <c r="D24" s="8" t="inlineStr">
         <is>
           <t>máme jen účastníky (HC Nedvědice – HHK Velké Meziříčí), chybí výsledek / odveta  [torzo-audit]</t>
         </is>

--- a/data/S2002_03_FINAL.xlsx
+++ b/data/S2002_03_FINAL.xlsx
@@ -14571,7 +14571,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>30_Praha L40</t>
+          <t>Praha, 4. úroveň</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -14618,7 +14618,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>30_Praha L50</t>
+          <t>Praha, 5. úroveň</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -14660,7 +14660,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>30_Praha L50</t>
+          <t>Praha, 5. úroveň</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -14702,7 +14702,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>30_Praha L40 Základní část</t>
+          <t>Praha, 4. úroveň, Základní část</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -14757,7 +14757,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>30_Praha L40 finálová skupina</t>
+          <t>Praha, 4. úroveň finálová skupina</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -14804,7 +14804,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>30_Praha L40 skupina o 5.-8.místo</t>
+          <t>Praha, 4. úroveň, skupina o 5.-8.místo</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -15463,7 +15463,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>30_Středočeský L40</t>
+          <t>Středočeský, 4. úroveň</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -15510,7 +15510,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>30_Jihočeský L40</t>
+          <t>Jihočeský, 4. úroveň</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -15557,7 +15557,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>30_Jihočeský L40 základní část</t>
+          <t>Jihočeský, 4. úroveň, základní část</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -15617,7 +15617,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>30_Jihočeský L40 Finále</t>
+          <t>Jihočeský, 4. úroveň, Finále</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -15672,7 +15672,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>30_Ústecký L40</t>
+          <t>Ústecký, 4. úroveň</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -15714,7 +15714,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>30_Liberecký L40</t>
+          <t>Liberecký, 4. úroveň</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -15756,7 +15756,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>30_Karlovarský L40</t>
+          <t>Karlovarský, 4. úroveň</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -15798,7 +15798,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>30_Plzeňský L40</t>
+          <t>Plzeňský, 4. úroveň</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -15840,7 +15840,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>30_Východočeský L40</t>
+          <t>Východočeský, 4. úroveň</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -15887,7 +15887,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>30_Východočeský L40 skupina Pardubicko</t>
+          <t>Východočeský, 4. úroveň, skupina Pardubicko</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -15929,7 +15929,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>30_Východočeský L40 skupina Hradecko</t>
+          <t>Východočeský, 4. úroveň, skupina Hradecko</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -15971,7 +15971,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>30_Východočeský L40 finále</t>
+          <t>Východočeský, 4. úroveň, finále</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -16021,7 +16021,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>30_Východočeský L40 o udržení</t>
+          <t>Východočeský, 4. úroveň o udržení</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -16076,7 +16076,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>30_Zlínský L40</t>
+          <t>Zlínský, 4. úroveň</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -16118,7 +16118,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>30_Zlínský L40 základní část</t>
+          <t>Zlínský, 4. úroveň, základní část</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -16173,7 +16173,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>30_Zlínský L40 finále</t>
+          <t>Zlínský, 4. úroveň, finále</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -16223,7 +16223,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>30_Jihomoravský-Vysočina L40</t>
+          <t>Jihomoravský-Vysočina, 4. úroveň</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -16265,7 +16265,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>30_Jihomoravský-Vysočina L40 základní část</t>
+          <t>Jihomoravský-Vysočina, 4. úroveň, základní část</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -16320,7 +16320,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>30_Jihomoravský-Vysočina L40 finále</t>
+          <t>Jihomoravský-Vysočina, 4. úroveň, finále</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -16370,7 +16370,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>30_Severomoravský L40</t>
+          <t>Severomoravský, 4. úroveň</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -16417,7 +16417,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>30_Severomoravský L40 základní část</t>
+          <t>Severomoravský, 4. úroveň, základní část</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -16477,7 +16477,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>30_Severomoravský L40 finále</t>
+          <t>Severomoravský, 4. úroveň, finále</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -16524,6 +16524,8 @@
         <v>5</v>
       </c>
     </row>
+    <row r="71"/>
+    <row r="72"/>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
@@ -16556,7 +16558,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>I.ČNHL (12 CZ) + SNHL (12 SVK)</t>
+          <t>I.ČNHL (12 CZ) + SNHL (12 Slovensko)</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -16653,6 +16655,7 @@
         </is>
       </c>
     </row>
+    <row r="80"/>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>

--- a/data/S2002_03_FINAL.xlsx
+++ b/data/S2002_03_FINAL.xlsx
@@ -6185,7 +6185,7 @@
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>udržel se</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
@@ -6457,7 +6457,7 @@
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>udržel se</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
@@ -16524,8 +16524,6 @@
         <v>5</v>
       </c>
     </row>
-    <row r="71"/>
-    <row r="72"/>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
@@ -16655,7 +16653,6 @@
         </is>
       </c>
     </row>
-    <row r="80"/>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
@@ -31377,7 +31374,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>postup</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -31455,7 +31452,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -31533,7 +31530,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -31616,7 +31613,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -31694,7 +31691,7 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -31767,7 +31764,7 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -31845,7 +31842,7 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -31923,7 +31920,7 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -32001,7 +31998,7 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -32084,7 +32081,7 @@
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>zanik</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -32162,7 +32159,7 @@
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>o udržení</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
@@ -32240,7 +32237,7 @@
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>o udržení</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
@@ -32323,7 +32320,7 @@
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>o udržení</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
@@ -32401,7 +32398,7 @@
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>sestup</t>
+          <t>o udržení</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
@@ -32851,7 +32848,7 @@
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>udržel se</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
@@ -32934,7 +32931,7 @@
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>udržel se</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
@@ -33012,7 +33009,7 @@
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>udržel se</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
@@ -33205,7 +33202,7 @@
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>udržel se</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
@@ -33283,7 +33280,7 @@
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>udržel se</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
@@ -33439,7 +33436,7 @@
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>udržel se</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
@@ -35186,7 +35183,7 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>o udržení</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -35264,7 +35261,7 @@
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>o udržení</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -35347,7 +35344,7 @@
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>o udržení</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
@@ -35425,7 +35422,7 @@
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>o udržení</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
@@ -35545,7 +35542,7 @@
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>udržel se</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
@@ -35623,7 +35620,7 @@
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>udržel se</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
@@ -35701,7 +35698,7 @@
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>udržel se</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
@@ -35779,7 +35776,7 @@
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>udržel se</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
@@ -36877,7 +36874,7 @@
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>udržel se</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
@@ -36955,7 +36952,7 @@
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>udržel se</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
@@ -37033,7 +37030,7 @@
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>udržel se</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
@@ -37111,7 +37108,7 @@
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>udržel se</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
@@ -40566,7 +40563,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
